--- a/daxpay-multi/daxpay-multi-service/src/main/resources/template/对账单模板.xlsx
+++ b/daxpay-multi/daxpay-multi-service/src/main/resources/template/对账单模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12270" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12270"/>
   </bookViews>
   <sheets>
     <sheet name="对账单概览" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>对账单</t>
   </si>
@@ -95,52 +95,55 @@
     <t>平台交易号</t>
   </si>
   <si>
+    <t>平台交易信息</t>
+  </si>
+  <si>
     <t>商户交易号</t>
   </si>
   <si>
+    <t>交易类型</t>
+  </si>
+  <si>
+    <t>交易金额</t>
+  </si>
+  <si>
+    <t>交易时间</t>
+  </si>
+  <si>
+    <t>交易状态</t>
+  </si>
+  <si>
+    <t>关联通道交易号</t>
+  </si>
+  <si>
     <t>通道交易号</t>
   </si>
   <si>
-    <t>平台交易信息</t>
-  </si>
-  <si>
-    <t>通道交易信息</t>
-  </si>
-  <si>
-    <t>交易类型</t>
-  </si>
-  <si>
-    <t>交易金额</t>
-  </si>
-  <si>
-    <t>交易时间</t>
-  </si>
-  <si>
-    <t>交易状态</t>
-  </si>
-  <si>
     <t>{{$fe: trades t.tradeNo</t>
   </si>
   <si>
+    <t>t.result</t>
+  </si>
+  <si>
     <t>t.bizTradeNo</t>
   </si>
   <si>
+    <t>t.tradeType</t>
+  </si>
+  <si>
+    <t>t.tradeAmount</t>
+  </si>
+  <si>
+    <t>t.tradeTime</t>
+  </si>
+  <si>
+    <t>t.tradeStatus</t>
+  </si>
+  <si>
     <t>t.outTradeNo</t>
   </si>
   <si>
-    <t>t.result</t>
-  </si>
-  <si>
-    <t>t.tradeType</t>
-  </si>
-  <si>
-    <t>t.tradeAmount</t>
-  </si>
-  <si>
-    <t>t.tradeTime</t>
-  </si>
-  <si>
-    <t>t.tradeStatus</t>
+    <t>t.channelTradeNo</t>
   </si>
   <si>
     <t>t.channelTradeType</t>
@@ -160,13 +163,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,97 +178,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,11 +243,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,6 +305,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -317,16 +358,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,25 +374,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,157 +536,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,43 +583,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -602,24 +612,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,9 +633,50 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,10 +688,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -667,157 +700,172 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,7 +1200,7 @@
     <col min="8" max="8" width="32.8454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="23" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1164,137 +1212,137 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" ht="14.5" spans="1:8">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="6" customFormat="1" ht="18.5" spans="1:8">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
-    <row r="3" ht="14.5" spans="1:8">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="6" customFormat="1" ht="18.5" spans="1:8">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
-    <row r="4" ht="14.5" spans="1:8">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="6" customFormat="1" ht="18.5" spans="1:8">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
-    <row r="5" ht="14.5" spans="1:8">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="6" customFormat="1" ht="18.5" spans="1:8">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="17.5" spans="1:8">
+      <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+    <row r="7" s="6" customFormat="1" ht="17.5" spans="1:8">
+      <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+    <row r="8" s="6" customFormat="1" ht="17.5" spans="1:8">
+      <c r="A8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+    <row r="9" s="6" customFormat="1" ht="17.5" spans="1:8">
+      <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1317,136 +1365,141 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="9.22727272727273" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="14.2636363636364" customWidth="1"/>
-    <col min="2" max="2" width="19.5454545454545" customWidth="1"/>
-    <col min="3" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="20.0272727272727" customWidth="1"/>
-    <col min="7" max="7" width="16.0272727272727" customWidth="1"/>
-    <col min="8" max="9" width="17.6181818181818" customWidth="1"/>
-    <col min="10" max="10" width="15.3727272727273" customWidth="1"/>
-    <col min="11" max="11" width="16.9818181818182" customWidth="1"/>
-    <col min="12" max="12" width="15.5363636363636" customWidth="1"/>
+    <col min="1" max="1" width="28.7272727272727" customWidth="1"/>
+    <col min="2" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="20.0272727272727" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="15.3727272727273" customWidth="1"/>
+    <col min="10" max="12" width="16.9818181818182" customWidth="1"/>
+    <col min="13" max="13" width="15.5363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="23" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A3" s="5"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="F3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="4:12">
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
+      <c r="A4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="5" t="s">
         <v>45</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="J2:L2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:M2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
